--- a/data_group/contrast_PF_SF_temp.xlsx
+++ b/data_group/contrast_PF_SF_temp.xlsx
@@ -428,19 +428,19 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.1608938464200372</v>
+        <v>0.1663001869926501</v>
       </c>
       <c r="E2">
-        <v>0.04248324831708114</v>
+        <v>0.02498684769299502</v>
       </c>
       <c r="F2">
-        <v>702.0007906186563</v>
+        <v>662</v>
       </c>
       <c r="G2">
-        <v>-3.78723032709688</v>
+        <v>-6.655508891554648</v>
       </c>
       <c r="H2">
-        <v>0.0004961451654702182</v>
+        <v>1.185310642568827E-10</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -475,19 +475,19 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.1986177157951486</v>
+        <v>0.1991894595148395</v>
       </c>
       <c r="E3">
-        <v>0.04248324831708113</v>
+        <v>0.02163644248020313</v>
       </c>
       <c r="F3">
-        <v>702.0007906265776</v>
+        <v>662</v>
       </c>
       <c r="G3">
-        <v>-4.675200782970517</v>
+        <v>-9.206201975999219</v>
       </c>
       <c r="H3">
-        <v>2.113206865435058E-05</v>
+        <v>2.625625359733245E-18</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -522,19 +522,19 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.1669959986742016</v>
+        <v>0.1938159986321334</v>
       </c>
       <c r="E4">
-        <v>0.04765622072999207</v>
+        <v>0.02417274889815328</v>
       </c>
       <c r="F4">
-        <v>702.0559947518638</v>
+        <v>662</v>
       </c>
       <c r="G4">
-        <v>-3.504180485069476</v>
+        <v>-8.017954410097744</v>
       </c>
       <c r="H4">
-        <v>0.0009741660657932808</v>
+        <v>1.463880989063832E-14</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -569,19 +569,19 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.0009108560671906633</v>
+        <v>0.008101447205285495</v>
       </c>
       <c r="E5">
-        <v>0.04248324831708114</v>
+        <v>0.02635989560620557</v>
       </c>
       <c r="F5">
-        <v>702.0007906319852</v>
+        <v>662</v>
       </c>
       <c r="G5">
-        <v>-0.02144035833588642</v>
+        <v>-0.3073398820053853</v>
       </c>
       <c r="H5">
-        <v>0.9829004721773746</v>
+        <v>0.7586813407884156</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="D6">
-        <v>-0.04312310177431745</v>
+        <v>-0.04497624026396216</v>
       </c>
       <c r="E6">
-        <v>0.04248324831708113</v>
+        <v>0.02155042077240532</v>
       </c>
       <c r="F6">
-        <v>702.0007906344259</v>
+        <v>662</v>
       </c>
       <c r="G6">
-        <v>1.015061311989626</v>
+        <v>2.087023763431706</v>
       </c>
       <c r="H6">
-        <v>0.3725115780245444</v>
+        <v>0.07374754853232381</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -653,19 +653,19 @@
         </is>
       </c>
       <c r="D7">
-        <v>-0.1146365628704847</v>
+        <v>-0.09588523690492323</v>
       </c>
       <c r="E7">
-        <v>0.04765622072999207</v>
+        <v>0.02219677871393929</v>
       </c>
       <c r="F7">
-        <v>702.0559947525674</v>
+        <v>662</v>
       </c>
       <c r="G7">
-        <v>2.405490009792973</v>
+        <v>4.319781628705815</v>
       </c>
       <c r="H7">
-        <v>0.04922535474622728</v>
+        <v>0.0001080857342483085</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -700,19 +700,19 @@
         </is>
       </c>
       <c r="D8">
-        <v>-0.1012954294183669</v>
+        <v>-0.09744380920316292</v>
       </c>
       <c r="E8">
-        <v>0.04248324831708118</v>
+        <v>0.02830347140405973</v>
       </c>
       <c r="F8">
-        <v>702.0007906307935</v>
+        <v>662</v>
       </c>
       <c r="G8">
-        <v>2.384361682099512</v>
+        <v>3.442821829593171</v>
       </c>
       <c r="H8">
-        <v>0.02606010691913399</v>
+        <v>0.0009179096117314893</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -747,19 +747,19 @@
         </is>
       </c>
       <c r="D9">
-        <v>-0.1522335083845469</v>
+        <v>-0.1579808669619177</v>
       </c>
       <c r="E9">
-        <v>0.04248324831708118</v>
+        <v>0.0213758241974434</v>
       </c>
       <c r="F9">
-        <v>702.0007906307409</v>
+        <v>662</v>
       </c>
       <c r="G9">
-        <v>3.583377317297524</v>
+        <v>7.390632777603619</v>
       </c>
       <c r="H9">
-        <v>0.001087898479820116</v>
+        <v>1.327105158010024E-12</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -794,19 +794,19 @@
         </is>
       </c>
       <c r="D10">
-        <v>-0.232580551468482</v>
+        <v>-0.2221663566303279</v>
       </c>
       <c r="E10">
-        <v>0.04765622072999209</v>
+        <v>0.02228528178708202</v>
       </c>
       <c r="F10">
-        <v>702.0559947499238</v>
+        <v>662</v>
       </c>
       <c r="G10">
-        <v>4.880381782395705</v>
+        <v>9.96919665422897</v>
       </c>
       <c r="H10">
-        <v>7.868576820729995E-06</v>
+        <v>3.98451521038084E-21</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -841,19 +841,19 @@
         </is>
       </c>
       <c r="D11">
-        <v>-0.08780655714097323</v>
+        <v>-0.08739475155658316</v>
       </c>
       <c r="E11">
-        <v>0.04248324831708114</v>
+        <v>0.0309128916204281</v>
       </c>
       <c r="F11">
-        <v>702.0007906194967</v>
+        <v>662</v>
       </c>
       <c r="G11">
-        <v>2.06685130302687</v>
+        <v>2.827129620537674</v>
       </c>
       <c r="H11">
-        <v>0.0391142583540483</v>
+        <v>0.005806294158110338</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -888,19 +888,19 @@
         </is>
       </c>
       <c r="D12">
-        <v>-0.1862644328110661</v>
+        <v>-0.1980449359464602</v>
       </c>
       <c r="E12">
-        <v>0.04248324831708114</v>
+        <v>0.02324216407196071</v>
       </c>
       <c r="F12">
-        <v>702.0007906186389</v>
+        <v>662</v>
       </c>
       <c r="G12">
-        <v>4.38442068791089</v>
+        <v>8.520933564245039</v>
       </c>
       <c r="H12">
-        <v>3.461639476094352E-05</v>
+        <v>3.199930426475147E-16</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -935,19 +935,19 @@
         </is>
       </c>
       <c r="D13">
-        <v>-0.2940160899019401</v>
+        <v>-0.2810980689714488</v>
       </c>
       <c r="E13">
-        <v>0.04765622072999206</v>
+        <v>0.02479825354830044</v>
       </c>
       <c r="F13">
-        <v>702.055994749285</v>
+        <v>662</v>
       </c>
       <c r="G13">
-        <v>6.169521741301308</v>
+        <v>11.33539781033144</v>
       </c>
       <c r="H13">
-        <v>6.941181421618533E-09</v>
+        <v>1.448003358325992E-26</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -982,19 +982,19 @@
         </is>
       </c>
       <c r="D14">
-        <v>-0.109814566184833</v>
+        <v>-0.109136212944984</v>
       </c>
       <c r="E14">
-        <v>0.04248324831708118</v>
+        <v>0.03191375613099446</v>
       </c>
       <c r="F14">
-        <v>702.0007906201287</v>
+        <v>662</v>
       </c>
       <c r="G14">
-        <v>2.584890999040674</v>
+        <v>3.41972322208076</v>
       </c>
       <c r="H14">
-        <v>0.01491238737095119</v>
+        <v>0.0009980004897001673</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1029,19 +1029,19 @@
         </is>
       </c>
       <c r="D15">
-        <v>-0.2080627159799688</v>
+        <v>-0.2110016220442419</v>
       </c>
       <c r="E15">
-        <v>0.04248324831708117</v>
+        <v>0.02357170262321644</v>
       </c>
       <c r="F15">
-        <v>702.0007906241515</v>
+        <v>662</v>
       </c>
       <c r="G15">
-        <v>4.897523711629964</v>
+        <v>8.951479891674028</v>
       </c>
       <c r="H15">
-        <v>3.616672584369843E-06</v>
+        <v>1.051674462666256E-17</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1076,19 +1076,19 @@
         </is>
       </c>
       <c r="D16">
-        <v>-0.3193570349204464</v>
+        <v>-0.3148001707511623</v>
       </c>
       <c r="E16">
-        <v>0.04765622072999209</v>
+        <v>0.02474293759061223</v>
       </c>
       <c r="F16">
-        <v>702.0559947468287</v>
+        <v>662</v>
       </c>
       <c r="G16">
-        <v>6.701266487954245</v>
+        <v>12.72282927596282</v>
       </c>
       <c r="H16">
-        <v>2.545893072366703E-10</v>
+        <v>1.495926763755903E-32</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1123,19 +1123,19 @@
         </is>
       </c>
       <c r="D17">
-        <v>-0.1573132322195129</v>
+        <v>-0.1596417419569154</v>
       </c>
       <c r="E17">
-        <v>0.04248324831708118</v>
+        <v>0.05830337385591324</v>
       </c>
       <c r="F17">
-        <v>702.0007906196771</v>
+        <v>662</v>
       </c>
       <c r="G17">
-        <v>3.702947360460245</v>
+        <v>2.738121851257571</v>
       </c>
       <c r="H17">
-        <v>0.0004596656708102436</v>
+        <v>0.01269045309127325</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1170,19 +1170,19 @@
         </is>
       </c>
       <c r="D18">
-        <v>-0.1616225375951189</v>
+        <v>-0.166528002220088</v>
       </c>
       <c r="E18">
-        <v>0.04248324831708117</v>
+        <v>0.02280205353361949</v>
       </c>
       <c r="F18">
-        <v>702.0007906240996</v>
+        <v>662</v>
       </c>
       <c r="G18">
-        <v>3.804382762561393</v>
+        <v>7.303201967075379</v>
       </c>
       <c r="H18">
-        <v>0.0004596656708102436</v>
+        <v>2.429094874832081E-12</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1217,19 +1217,19 @@
         </is>
       </c>
       <c r="D19">
-        <v>-0.2582214791991445</v>
+        <v>-0.255881432473565</v>
       </c>
       <c r="E19">
-        <v>0.04765622072999209</v>
+        <v>0.02681494109719126</v>
       </c>
       <c r="F19">
-        <v>702.0559947465871</v>
+        <v>662</v>
       </c>
       <c r="G19">
-        <v>5.418421252120705</v>
+        <v>9.54249466915172</v>
       </c>
       <c r="H19">
-        <v>4.962500613525777E-07</v>
+        <v>1.574615606172904E-19</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1264,19 +1264,19 @@
         </is>
       </c>
       <c r="D20">
-        <v>-0.1948353891715255</v>
+        <v>-0.2062325279391882</v>
       </c>
       <c r="E20">
-        <v>0.04248324831708115</v>
+        <v>0.04708295078925331</v>
       </c>
       <c r="F20">
-        <v>702.0007906194126</v>
+        <v>662</v>
       </c>
       <c r="G20">
-        <v>4.586169770195949</v>
+        <v>4.380195473777756</v>
       </c>
       <c r="H20">
-        <v>1.603671643056064E-05</v>
+        <v>2.756356123147079E-05</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1311,19 +1311,19 @@
         </is>
       </c>
       <c r="D21">
-        <v>-0.1545150601711282</v>
+        <v>-0.1691735350789924</v>
       </c>
       <c r="E21">
-        <v>0.04248324831708114</v>
+        <v>0.02392467127334339</v>
       </c>
       <c r="F21">
-        <v>702.0007906187798</v>
+        <v>662</v>
       </c>
       <c r="G21">
-        <v>3.637082056858696</v>
+        <v>7.071091307636221</v>
       </c>
       <c r="H21">
-        <v>0.0005918675333046361</v>
+        <v>1.174910971543479E-11</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1358,19 +1358,19 @@
         </is>
       </c>
       <c r="D22">
-        <v>-0.2585051310471044</v>
+        <v>-0.2452898636698581</v>
       </c>
       <c r="E22">
-        <v>0.04765622072999207</v>
+        <v>0.02267063397534743</v>
       </c>
       <c r="F22">
-        <v>702.0559947491857</v>
+        <v>662</v>
       </c>
       <c r="G22">
-        <v>5.424373294553259</v>
+        <v>10.81971787540622</v>
       </c>
       <c r="H22">
-        <v>4.806400938781817E-07</v>
+        <v>1.863413450286718E-24</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1405,19 +1405,19 @@
         </is>
       </c>
       <c r="D23">
-        <v>-0.2628884929275528</v>
+        <v>-0.2353974535151173</v>
       </c>
       <c r="E23">
-        <v>0.04248324831708116</v>
+        <v>0.06561674584821391</v>
       </c>
       <c r="F23">
-        <v>702.0007906306813</v>
+        <v>662</v>
       </c>
       <c r="G23">
-        <v>6.188050663297649</v>
+        <v>3.587460037406363</v>
       </c>
       <c r="H23">
-        <v>3.105201889231839E-09</v>
+        <v>0.0007170770423534251</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1452,19 +1452,19 @@
         </is>
       </c>
       <c r="D24">
-        <v>-0.269995220231421</v>
+        <v>-0.2631301654930145</v>
       </c>
       <c r="E24">
-        <v>0.04248324831708116</v>
+        <v>0.03110967358569483</v>
       </c>
       <c r="F24">
-        <v>702.0007906307254</v>
+        <v>662</v>
       </c>
       <c r="G24">
-        <v>6.355333712155541</v>
+        <v>8.458146137991294</v>
       </c>
       <c r="H24">
-        <v>2.244991489049634E-09</v>
+        <v>1.041717330088416E-15</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1499,19 +1499,19 @@
         </is>
       </c>
       <c r="D25">
-        <v>-0.2805825527428978</v>
+        <v>-0.2864296922232548</v>
       </c>
       <c r="E25">
-        <v>0.04765622072999208</v>
+        <v>0.03450165665440942</v>
       </c>
       <c r="F25">
-        <v>702.0559947499396</v>
+        <v>662</v>
       </c>
       <c r="G25">
-        <v>5.887637509751489</v>
+        <v>8.301911270299776</v>
       </c>
       <c r="H25">
-        <v>1.214272276035297E-08</v>
+        <v>1.729379848014325E-15</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1546,19 +1546,19 @@
         </is>
       </c>
       <c r="D26">
-        <v>-0.02454106496961845</v>
+        <v>-0.02023757266897228</v>
       </c>
       <c r="E26">
-        <v>0.04361595159682789</v>
+        <v>0.07166650400681006</v>
       </c>
       <c r="F26">
-        <v>702.0096773496819</v>
+        <v>662</v>
       </c>
       <c r="G26">
-        <v>0.5626626055638615</v>
+        <v>0.282385375838191</v>
       </c>
       <c r="H26">
-        <v>0.5738442857415618</v>
+        <v>0.7777362907892795</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1588,19 +1588,19 @@
         </is>
       </c>
       <c r="D27">
-        <v>-0.2076309579700001</v>
+        <v>-0.146339669556236</v>
       </c>
       <c r="E27">
-        <v>0.04248324831708111</v>
+        <v>0.03413892877435945</v>
       </c>
       <c r="F27">
-        <v>702.0007906342153</v>
+        <v>662</v>
       </c>
       <c r="G27">
-        <v>4.887360693803597</v>
+        <v>4.286592310012567</v>
       </c>
       <c r="H27">
-        <v>2.534599056327734E-06</v>
+        <v>6.252375148178215E-05</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -1635,19 +1635,19 @@
         </is>
       </c>
       <c r="D28">
-        <v>-0.2686221031581024</v>
+        <v>-0.2543952743722964</v>
       </c>
       <c r="E28">
-        <v>0.04765622072999205</v>
+        <v>0.02963367594278779</v>
       </c>
       <c r="F28">
-        <v>702.0559947522847</v>
+        <v>662</v>
       </c>
       <c r="G28">
-        <v>5.63666398726929</v>
+        <v>8.584668161433775</v>
       </c>
       <c r="H28">
-        <v>1.507252473428101E-07</v>
+        <v>3.891863930160028E-16</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -1682,19 +1682,19 @@
         </is>
       </c>
       <c r="D29">
-        <v>-0.6978978930244942</v>
+        <v>-0.6211061005782663</v>
       </c>
       <c r="E29">
-        <v>0.04664445661657764</v>
+        <v>0.07246929062962125</v>
       </c>
       <c r="F29">
-        <v>702.0323986878828</v>
+        <v>662</v>
       </c>
       <c r="G29">
-        <v>14.96207574591958</v>
+        <v>8.570611015811352</v>
       </c>
       <c r="H29">
-        <v>2.33988848336753E-43</v>
+        <v>2.172091743371204E-16</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -1729,19 +1729,19 @@
         </is>
       </c>
       <c r="D30">
-        <v>-0.498231820538882</v>
+        <v>-0.4049419246414218</v>
       </c>
       <c r="E30">
-        <v>0.04248324831708113</v>
+        <v>0.0755165573720632</v>
       </c>
       <c r="F30">
-        <v>702.0007906264992</v>
+        <v>662</v>
       </c>
       <c r="G30">
-        <v>11.72772422721168</v>
+        <v>5.362293233870683</v>
       </c>
       <c r="H30">
-        <v>1.178511967095131E-28</v>
+        <v>2.273308520948701E-07</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -1776,19 +1776,19 @@
         </is>
       </c>
       <c r="D31">
-        <v>-0.3888184651512215</v>
+        <v>-0.3532272062089181</v>
       </c>
       <c r="E31">
-        <v>0.04765622072999205</v>
+        <v>0.03099827260124843</v>
       </c>
       <c r="F31">
-        <v>702.0559947523816</v>
+        <v>662</v>
       </c>
       <c r="G31">
-        <v>8.158818706044011</v>
+        <v>11.39506096848416</v>
       </c>
       <c r="H31">
-        <v>3.123946665140193E-15</v>
+        <v>8.174973195909262E-27</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -1823,19 +1823,19 @@
         </is>
       </c>
       <c r="D32">
-        <v>-0.3113427332393606</v>
+        <v>-0.307602831433904</v>
       </c>
       <c r="E32">
-        <v>0.02293262676423211</v>
+        <v>0.0330530618303691</v>
       </c>
       <c r="F32">
-        <v>709.9967077514315</v>
+        <v>670</v>
       </c>
       <c r="G32">
-        <v>13.57640956006662</v>
+        <v>9.30633394910722</v>
       </c>
       <c r="H32">
-        <v>1.027729515945479E-36</v>
+        <v>6.336293277816423E-19</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -1870,19 +1870,19 @@
         </is>
       </c>
       <c r="D33">
-        <v>-0.3082187382899958</v>
+        <v>-0.304011184009561</v>
       </c>
       <c r="E33">
-        <v>0.02293262676423211</v>
+        <v>0.03429428818341924</v>
       </c>
       <c r="F33">
-        <v>709.9967077491265</v>
+        <v>670</v>
       </c>
       <c r="G33">
-        <v>13.44018465301684</v>
+        <v>8.864776034527686</v>
       </c>
       <c r="H33">
-        <v>2.239027881860957E-36</v>
+        <v>1.375009873239656E-17</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -1917,19 +1917,19 @@
         </is>
       </c>
       <c r="D34">
-        <v>-0.3391151171156749</v>
+        <v>-0.3209572906482495</v>
       </c>
       <c r="E34">
-        <v>0.02572462894015591</v>
+        <v>0.0345463964141842</v>
       </c>
       <c r="F34">
-        <v>710.0132756927645</v>
+        <v>670</v>
       </c>
       <c r="G34">
-        <v>13.18250762351403</v>
+        <v>9.290615634702482</v>
       </c>
       <c r="H34">
-        <v>2.358485606501766E-35</v>
+        <v>6.336293277816423E-19</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -1964,19 +1964,19 @@
         </is>
       </c>
       <c r="D35">
-        <v>-0.3759633104291444</v>
+        <v>-0.3750000969518541</v>
       </c>
       <c r="E35">
-        <v>0.0229326267642321</v>
+        <v>0.02854305318279889</v>
       </c>
       <c r="F35">
-        <v>709.9967077489358</v>
+        <v>670</v>
       </c>
       <c r="G35">
-        <v>16.39425410330806</v>
+        <v>13.13805129921571</v>
       </c>
       <c r="H35">
-        <v>5.460109312397017E-51</v>
+        <v>9.080147162514261E-35</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -2011,19 +2011,19 @@
         </is>
       </c>
       <c r="D36">
-        <v>-0.396638866848382</v>
+        <v>-0.3826283779900767</v>
       </c>
       <c r="E36">
-        <v>0.0229326267642321</v>
+        <v>0.02987545613668786</v>
       </c>
       <c r="F36">
-        <v>709.9967077453167</v>
+        <v>670</v>
       </c>
       <c r="G36">
-        <v>17.29583230591873</v>
+        <v>12.80744890519675</v>
       </c>
       <c r="H36">
-        <v>2.041829638652201E-55</v>
+        <v>1.902682462460074E-33</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -2058,19 +2058,19 @@
         </is>
       </c>
       <c r="D37">
-        <v>-0.4028222722035315</v>
+        <v>-0.3923339425291817</v>
       </c>
       <c r="E37">
-        <v>0.0257246289401559</v>
+        <v>0.02925651665777034</v>
       </c>
       <c r="F37">
-        <v>710.0132756932336</v>
+        <v>670</v>
       </c>
       <c r="G37">
-        <v>15.65901195856434</v>
+        <v>13.41013857249408</v>
       </c>
       <c r="H37">
-        <v>2.153217731726061E-47</v>
+        <v>1.023901318752366E-35</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -2105,19 +2105,19 @@
         </is>
       </c>
       <c r="D38">
-        <v>-0.3994662753529032</v>
+        <v>-0.3981327154039222</v>
       </c>
       <c r="E38">
-        <v>0.02293262676423213</v>
+        <v>0.02671335731848164</v>
       </c>
       <c r="F38">
-        <v>709.9967077483398</v>
+        <v>670</v>
       </c>
       <c r="G38">
-        <v>17.41912426604126</v>
+        <v>14.90388162960236</v>
       </c>
       <c r="H38">
-        <v>2.261149571384048E-56</v>
+        <v>8.113560156796143E-43</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -2152,19 +2152,19 @@
         </is>
       </c>
       <c r="D39">
-        <v>-0.4116221734303079</v>
+        <v>-0.3912830767827016</v>
       </c>
       <c r="E39">
-        <v>0.02293262676423213</v>
+        <v>0.02733236895280441</v>
       </c>
       <c r="F39">
-        <v>709.9967077474171</v>
+        <v>670</v>
       </c>
       <c r="G39">
-        <v>17.94919429257499</v>
+        <v>14.31573960743547</v>
       </c>
       <c r="H39">
-        <v>6.612162845870665E-59</v>
+        <v>2.82631625866093E-40</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -2199,19 +2199,19 @@
         </is>
       </c>
       <c r="D40">
-        <v>-0.376281771157321</v>
+        <v>-0.370732917127473</v>
       </c>
       <c r="E40">
-        <v>0.02572462894015593</v>
+        <v>0.02602969136453025</v>
       </c>
       <c r="F40">
-        <v>710.0132756933951</v>
+        <v>670</v>
       </c>
       <c r="G40">
-        <v>14.62729635605932</v>
+        <v>14.24269354313812</v>
       </c>
       <c r="H40">
-        <v>3.040617778196677E-42</v>
+        <v>4.208311123480789E-40</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -2246,19 +2246,19 @@
         </is>
       </c>
       <c r="D41">
-        <v>-0.3696313280706108</v>
+        <v>-0.3658706819730906</v>
       </c>
       <c r="E41">
-        <v>0.02293262676423211</v>
+        <v>0.02399536346382348</v>
       </c>
       <c r="F41">
-        <v>709.9967077473482</v>
+        <v>670</v>
       </c>
       <c r="G41">
-        <v>16.11814171445561</v>
+        <v>15.24755740935928</v>
       </c>
       <c r="H41">
-        <v>1.455794278842008E-49</v>
+        <v>5.554241993034848E-45</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -2293,19 +2293,19 @@
         </is>
       </c>
       <c r="D42">
-        <v>-0.3944107876606689</v>
+        <v>-0.374019553213032</v>
       </c>
       <c r="E42">
-        <v>0.02293262676423211</v>
+        <v>0.0234837427037759</v>
       </c>
       <c r="F42">
-        <v>709.996707746457</v>
+        <v>670</v>
       </c>
       <c r="G42">
-        <v>17.1986746967787</v>
+        <v>15.92674378743275</v>
       </c>
       <c r="H42">
-        <v>6.677243567951735E-55</v>
+        <v>3.412792352675643E-48</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -2340,19 +2340,19 @@
         </is>
       </c>
       <c r="D43">
-        <v>-0.3540530086560633</v>
+        <v>-0.3490069928978426</v>
       </c>
       <c r="E43">
-        <v>0.02572462894015591</v>
+        <v>0.02179974184173759</v>
       </c>
       <c r="F43">
-        <v>710.0132756911638</v>
+        <v>670</v>
       </c>
       <c r="G43">
-        <v>13.76319205535322</v>
+        <v>16.00968467569817</v>
       </c>
       <c r="H43">
-        <v>4.48947579511358E-38</v>
+        <v>2.605518939246406E-48</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -2387,19 +2387,19 @@
         </is>
       </c>
       <c r="D44">
-        <v>-0.2678305185392723</v>
+        <v>-0.2597782433125958</v>
       </c>
       <c r="E44">
-        <v>0.02293262676423213</v>
+        <v>0.02144610345075351</v>
       </c>
       <c r="F44">
-        <v>709.9967077499015</v>
+        <v>670</v>
       </c>
       <c r="G44">
-        <v>11.67901615862888</v>
+        <v>12.11307424255983</v>
       </c>
       <c r="H44">
-        <v>1.79479293418942E-28</v>
+        <v>2.233684876397262E-30</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -2434,19 +2434,19 @@
         </is>
       </c>
       <c r="D45">
-        <v>-0.306920436026237</v>
+        <v>-0.288129557810525</v>
       </c>
       <c r="E45">
-        <v>0.02293262676423213</v>
+        <v>0.02052484801174871</v>
       </c>
       <c r="F45">
-        <v>709.996707748117</v>
+        <v>670</v>
       </c>
       <c r="G45">
-        <v>13.38357089144881</v>
+        <v>14.03808484455503</v>
       </c>
       <c r="H45">
-        <v>8.234431103696566E-36</v>
+        <v>1.185005431988786E-38</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -2481,19 +2481,19 @@
         </is>
       </c>
       <c r="D46">
-        <v>-0.2722122335323744</v>
+        <v>-0.2570184868376756</v>
       </c>
       <c r="E46">
-        <v>0.02572462894015592</v>
+        <v>0.01853257354088864</v>
       </c>
       <c r="F46">
-        <v>710.013275692118</v>
+        <v>670</v>
       </c>
       <c r="G46">
-        <v>10.58177492727421</v>
+        <v>13.86847251789465</v>
       </c>
       <c r="H46">
-        <v>4.249577181204902E-24</v>
+        <v>3.742156186312189E-38</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -2528,19 +2528,19 @@
         </is>
       </c>
       <c r="D47">
-        <v>-0.2343543616762016</v>
+        <v>-0.2223399684703717</v>
       </c>
       <c r="E47">
-        <v>0.02293262676423213</v>
+        <v>0.02300616573383737</v>
       </c>
       <c r="F47">
-        <v>709.9967077499012</v>
+        <v>670</v>
       </c>
       <c r="G47">
-        <v>10.21925504154293</v>
+        <v>9.664364372693145</v>
       </c>
       <c r="H47">
-        <v>1.73088786331841E-22</v>
+        <v>1.797020781674973E-20</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -2575,19 +2575,19 @@
         </is>
       </c>
       <c r="D48">
-        <v>-0.2566945544070707</v>
+        <v>-0.2318774942961031</v>
       </c>
       <c r="E48">
-        <v>0.02293262676423213</v>
+        <v>0.02107954018883275</v>
       </c>
       <c r="F48">
-        <v>709.9967077481174</v>
+        <v>670</v>
       </c>
       <c r="G48">
-        <v>11.19342136625341</v>
+        <v>11.00012107564586</v>
       </c>
       <c r="H48">
-        <v>4.044528913988977E-26</v>
+        <v>1.64245156721669E-25</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -2622,19 +2622,19 @@
         </is>
       </c>
       <c r="D49">
-        <v>-0.2310243177668148</v>
+        <v>-0.2149526608651869</v>
       </c>
       <c r="E49">
-        <v>0.02572462894015592</v>
+        <v>0.01857530619485727</v>
       </c>
       <c r="F49">
-        <v>710.0132756921645</v>
+        <v>670</v>
       </c>
       <c r="G49">
-        <v>8.980666671781915</v>
+        <v>11.57195787839548</v>
       </c>
       <c r="H49">
-        <v>4.780522595474614E-18</v>
+        <v>1.391377052301467E-27</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -2669,19 +2669,19 @@
         </is>
       </c>
       <c r="D50">
-        <v>-0.2820991550014964</v>
+        <v>-0.2694912940800291</v>
       </c>
       <c r="E50">
-        <v>0.02293262676423211</v>
+        <v>0.02397501687129597</v>
       </c>
       <c r="F50">
-        <v>709.9967077473478</v>
+        <v>670</v>
       </c>
       <c r="G50">
-        <v>12.30121424386869</v>
+        <v>11.24050487750342</v>
       </c>
       <c r="H50">
-        <v>3.478865984333026E-31</v>
+        <v>1.126134689947961E-26</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -2716,19 +2716,19 @@
         </is>
       </c>
       <c r="D51">
-        <v>-0.3002736391297183</v>
+        <v>-0.2781752795205685</v>
       </c>
       <c r="E51">
-        <v>0.02293262676423211</v>
+        <v>0.02280886912070394</v>
       </c>
       <c r="F51">
-        <v>709.9967077464567</v>
+        <v>670</v>
       </c>
       <c r="G51">
-        <v>13.09373070153714</v>
+        <v>12.19592598162023</v>
       </c>
       <c r="H51">
-        <v>1.818206082497179E-34</v>
+        <v>1.460137458247739E-30</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -2763,19 +2763,19 @@
         </is>
       </c>
       <c r="D52">
-        <v>-0.2809976416063142</v>
+        <v>-0.2639807587625255</v>
       </c>
       <c r="E52">
-        <v>0.0257246289401559</v>
+        <v>0.02011784442577412</v>
       </c>
       <c r="F52">
-        <v>710.0132756912062</v>
+        <v>670</v>
       </c>
       <c r="G52">
-        <v>10.92329231492547</v>
+        <v>13.12172184930134</v>
       </c>
       <c r="H52">
-        <v>1.759025684224322E-25</v>
+        <v>2.155783538207138E-34</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -2810,19 +2810,19 @@
         </is>
       </c>
       <c r="D53">
-        <v>-0.3464430788180218</v>
+        <v>-0.3357477822400245</v>
       </c>
       <c r="E53">
-        <v>0.02293262676423212</v>
+        <v>0.0235553330989593</v>
       </c>
       <c r="F53">
-        <v>709.9967077483395</v>
+        <v>670</v>
       </c>
       <c r="G53">
-        <v>15.1069950415958</v>
+        <v>14.25357819520107</v>
       </c>
       <c r="H53">
-        <v>1.935256715275767E-44</v>
+        <v>1.120177663996302E-39</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
@@ -2857,19 +2857,19 @@
         </is>
       </c>
       <c r="D54">
-        <v>-0.3593179876806023</v>
+        <v>-0.3346757485670423</v>
       </c>
       <c r="E54">
-        <v>0.02293262676423212</v>
+        <v>0.02465760596420752</v>
       </c>
       <c r="F54">
-        <v>709.9967077474172</v>
+        <v>670</v>
       </c>
       <c r="G54">
-        <v>15.66841824858147</v>
+        <v>13.57292143660868</v>
       </c>
       <c r="H54">
-        <v>5.789059042117222E-47</v>
+        <v>6.012381199165971E-37</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
@@ -2904,19 +2904,19 @@
         </is>
       </c>
       <c r="D55">
-        <v>-0.315888473650175</v>
+        <v>-0.2990658655951954</v>
       </c>
       <c r="E55">
-        <v>0.02572462894015592</v>
+        <v>0.02176398435159532</v>
       </c>
       <c r="F55">
-        <v>710.0132756935874</v>
+        <v>670</v>
       </c>
       <c r="G55">
-        <v>12.27961244397488</v>
+        <v>13.74131963907949</v>
       </c>
       <c r="H55">
-        <v>2.890533296585183E-31</v>
+        <v>1.478106372436918E-37</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
@@ -2951,19 +2951,19 @@
         </is>
       </c>
       <c r="D56">
-        <v>-0.4120485653655706</v>
+        <v>-0.3932408172207964</v>
       </c>
       <c r="E56">
-        <v>0.02293262676423211</v>
+        <v>0.02754181616572531</v>
       </c>
       <c r="F56">
-        <v>709.9967077489358</v>
+        <v>670</v>
       </c>
       <c r="G56">
-        <v>17.96778753702303</v>
+        <v>14.27795519564062</v>
       </c>
       <c r="H56">
-        <v>5.251931040563612E-59</v>
+        <v>8.568068604682889E-40</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
@@ -2998,19 +2998,19 @@
         </is>
       </c>
       <c r="D57">
-        <v>-0.3737669301469769</v>
+        <v>-0.3452529793661719</v>
       </c>
       <c r="E57">
-        <v>0.02293262676423211</v>
+        <v>0.0267388012383895</v>
       </c>
       <c r="F57">
-        <v>709.9967077453165</v>
+        <v>670</v>
       </c>
       <c r="G57">
-        <v>16.29847875647368</v>
+        <v>12.91205900698661</v>
       </c>
       <c r="H57">
-        <v>1.710158928995037E-50</v>
+        <v>6.4267907907258E-34</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
@@ -3045,19 +3045,19 @@
         </is>
       </c>
       <c r="D58">
-        <v>-0.3394039524724594</v>
+        <v>-0.3206888421566488</v>
       </c>
       <c r="E58">
-        <v>0.02572462894015591</v>
+        <v>0.02409092839314763</v>
       </c>
       <c r="F58">
-        <v>710.0132756931703</v>
+        <v>670</v>
       </c>
       <c r="G58">
-        <v>13.19373559331124</v>
+        <v>13.31160165034839</v>
       </c>
       <c r="H58">
-        <v>2.092595922851358E-35</v>
+        <v>1.456120150079219E-35</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
@@ -3092,19 +3092,19 @@
         </is>
       </c>
       <c r="D59">
-        <v>-0.8164594903065585</v>
+        <v>-0.8354433363187801</v>
       </c>
       <c r="E59">
-        <v>0.02293262676423211</v>
+        <v>0.03668134912233368</v>
       </c>
       <c r="F59">
-        <v>709.9967077514315</v>
+        <v>670</v>
       </c>
       <c r="G59">
-        <v>35.60252816655028</v>
+        <v>22.77569817654594</v>
       </c>
       <c r="H59">
-        <v>2.64889259634063E-159</v>
+        <v>1.066629288367873E-84</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
@@ -3139,19 +3139,19 @@
         </is>
       </c>
       <c r="D60">
-        <v>-0.7602733804035451</v>
+        <v>-0.7267940964554427</v>
       </c>
       <c r="E60">
-        <v>0.02293262676423211</v>
+        <v>0.03256461251166558</v>
       </c>
       <c r="F60">
-        <v>709.9967077491265</v>
+        <v>670</v>
       </c>
       <c r="G60">
-        <v>33.15247695869446</v>
+        <v>22.31852432437463</v>
       </c>
       <c r="H60">
-        <v>7.243790955091815E-146</v>
+        <v>1.893506495827805E-82</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
@@ -3186,19 +3186,19 @@
         </is>
       </c>
       <c r="D61">
-        <v>-0.667968191555953</v>
+        <v>-0.6631066349796281</v>
       </c>
       <c r="E61">
-        <v>0.02572462894015591</v>
+        <v>0.0297740712044151</v>
       </c>
       <c r="F61">
-        <v>710.013275692517</v>
+        <v>670</v>
       </c>
       <c r="G61">
-        <v>25.96609626944942</v>
+        <v>22.27127860436157</v>
       </c>
       <c r="H61">
-        <v>9.979260394347908E-105</v>
+        <v>2.313786671573884E-82</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
@@ -3233,19 +3233,19 @@
         </is>
       </c>
       <c r="D62">
-        <v>-0.5879622296130754</v>
+        <v>-0.5949399456711313</v>
       </c>
       <c r="E62">
-        <v>0.02891681708520618</v>
+        <v>0.02285436539063136</v>
       </c>
       <c r="F62">
-        <v>709.9961706941211</v>
+        <v>670</v>
       </c>
       <c r="G62">
-        <v>20.33288200013813</v>
+        <v>26.03178585370013</v>
       </c>
       <c r="H62">
-        <v>5.294579640017436E-72</v>
+        <v>5.518833525022667E-103</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -3280,19 +3280,19 @@
         </is>
       </c>
       <c r="D63">
-        <v>-0.5455889376747364</v>
+        <v>-0.5870711018783843</v>
       </c>
       <c r="E63">
-        <v>0.02891681708520618</v>
+        <v>0.02882921235325571</v>
       </c>
       <c r="F63">
-        <v>709.9961706967041</v>
+        <v>670</v>
       </c>
       <c r="G63">
-        <v>18.86753082357253</v>
+        <v>20.3637579370803</v>
       </c>
       <c r="H63">
-        <v>3.432042703210367E-64</v>
+        <v>8.057203288386103E-72</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
@@ -3327,19 +3327,19 @@
         </is>
       </c>
       <c r="D64">
-        <v>-0.5075040993999614</v>
+        <v>-0.531664779692528</v>
       </c>
       <c r="E64">
-        <v>0.03243734127430563</v>
+        <v>0.02503469860244831</v>
       </c>
       <c r="F64">
-        <v>710.0163590206319</v>
+        <v>670</v>
       </c>
       <c r="G64">
-        <v>15.64567499870796</v>
+        <v>21.23711525892039</v>
       </c>
       <c r="H64">
-        <v>2.516148282964948E-47</v>
+        <v>1.896010721924212E-76</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
@@ -3374,19 +3374,19 @@
         </is>
       </c>
       <c r="D65">
-        <v>-0.4527165245211942</v>
+        <v>-0.4625016154125048</v>
       </c>
       <c r="E65">
-        <v>0.02891681708520616</v>
+        <v>0.01689770355396558</v>
       </c>
       <c r="F65">
-        <v>709.9961706935276</v>
+        <v>670</v>
       </c>
       <c r="G65">
-        <v>15.65582142693028</v>
+        <v>27.37067873959501</v>
       </c>
       <c r="H65">
-        <v>2.235783243044061E-47</v>
+        <v>1.622584015502226E-110</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
@@ -3421,19 +3421,19 @@
         </is>
       </c>
       <c r="D66">
-        <v>-0.5336486275952218</v>
+        <v>-0.5707116554344784</v>
       </c>
       <c r="E66">
-        <v>0.02891681708520616</v>
+        <v>0.02840720746994847</v>
       </c>
       <c r="F66">
-        <v>709.996170695711</v>
+        <v>670</v>
       </c>
       <c r="G66">
-        <v>18.45461158545822</v>
+        <v>20.09038220452416</v>
       </c>
       <c r="H66">
-        <v>1.225060476403765E-61</v>
+        <v>2.51642415343779E-70</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
@@ -3468,19 +3468,19 @@
         </is>
       </c>
       <c r="D67">
-        <v>-0.5334351414359881</v>
+        <v>-0.568243843465754</v>
       </c>
       <c r="E67">
-        <v>0.03243734127430561</v>
+        <v>0.02484102118865404</v>
       </c>
       <c r="F67">
-        <v>710.0163590208614</v>
+        <v>670</v>
       </c>
       <c r="G67">
-        <v>16.44509446458655</v>
+        <v>22.8752207548253</v>
       </c>
       <c r="H67">
-        <v>2.973527467189367E-51</v>
+        <v>1.482287333169821E-85</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
@@ -3515,19 +3515,19 @@
         </is>
       </c>
       <c r="D68">
-        <v>-0.3437871748775572</v>
+        <v>-0.3441332485523338</v>
       </c>
       <c r="E68">
-        <v>0.0289168170852062</v>
+        <v>0.01389000815419301</v>
       </c>
       <c r="F68">
-        <v>709.9961706948852</v>
+        <v>670</v>
       </c>
       <c r="G68">
-        <v>11.88883181245554</v>
+        <v>24.77559730218369</v>
       </c>
       <c r="H68">
-        <v>1.490921807764162E-29</v>
+        <v>6.477890018135307E-96</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
@@ -3562,19 +3562,19 @@
         </is>
       </c>
       <c r="D69">
-        <v>-0.5046622590931951</v>
+        <v>-0.5340317547853893</v>
       </c>
       <c r="E69">
-        <v>0.0289168170852062</v>
+        <v>0.02802169305310247</v>
       </c>
       <c r="F69">
-        <v>709.9961706972845</v>
+        <v>670</v>
       </c>
       <c r="G69">
-        <v>17.45220636165311</v>
+        <v>19.05779760606803</v>
       </c>
       <c r="H69">
-        <v>3.015728943667913E-56</v>
+        <v>9.975644458029547E-65</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
@@ -3609,19 +3609,19 @@
         </is>
       </c>
       <c r="D70">
-        <v>-0.4851482177614027</v>
+        <v>-0.5255288439817171</v>
       </c>
       <c r="E70">
-        <v>0.03243734127430565</v>
+        <v>0.02222049644721371</v>
       </c>
       <c r="F70">
-        <v>710.0163590209374</v>
+        <v>670</v>
       </c>
       <c r="G70">
-        <v>14.95647296301992</v>
+        <v>23.6506346845196</v>
       </c>
       <c r="H70">
-        <v>1.084583316518452E-43</v>
+        <v>6.753662773544964E-90</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
@@ -3656,19 +3656,19 @@
         </is>
       </c>
       <c r="D71">
-        <v>-0.2279618025009501</v>
+        <v>-0.2185114466627709</v>
       </c>
       <c r="E71">
-        <v>0.02891681708520618</v>
+        <v>0.01500153786309142</v>
       </c>
       <c r="F71">
-        <v>709.9961706943607</v>
+        <v>670</v>
       </c>
       <c r="G71">
-        <v>7.883364266172129</v>
+        <v>14.56593641645094</v>
       </c>
       <c r="H71">
-        <v>2.40298685254996E-14</v>
+        <v>1.182524511599033E-41</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
@@ -3703,19 +3703,19 @@
         </is>
       </c>
       <c r="D72">
-        <v>-0.4157187017942787</v>
+        <v>-0.4299512990723405</v>
       </c>
       <c r="E72">
-        <v>0.02891681708520618</v>
+        <v>0.02533575316574882</v>
       </c>
       <c r="F72">
-        <v>709.9961706967568</v>
+        <v>670</v>
       </c>
       <c r="G72">
-        <v>14.37636447224892</v>
+        <v>16.97014082271641</v>
       </c>
       <c r="H72">
-        <v>1.531645097721548E-40</v>
+        <v>1.603811455785562E-53</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
@@ -3750,19 +3750,19 @@
         </is>
       </c>
       <c r="D73">
-        <v>-0.4316738633660369</v>
+        <v>-0.4702163375779734</v>
       </c>
       <c r="E73">
-        <v>0.03243734127430562</v>
+        <v>0.02180558716242563</v>
       </c>
       <c r="F73">
-        <v>710.0163590211387</v>
+        <v>670</v>
       </c>
       <c r="G73">
-        <v>13.30792988597915</v>
+        <v>21.56403008437344</v>
       </c>
       <c r="H73">
-        <v>9.266914279838086E-36</v>
+        <v>5.89159110143907E-78</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
@@ -3797,19 +3797,19 @@
         </is>
       </c>
       <c r="D74">
-        <v>-0.03803467046319848</v>
+        <v>-0.03002938724686866</v>
       </c>
       <c r="E74">
-        <v>0.02891681708520619</v>
+        <v>0.01434070056199089</v>
       </c>
       <c r="F74">
-        <v>709.9961706944199</v>
+        <v>670</v>
       </c>
       <c r="G74">
-        <v>1.31531317403038</v>
+        <v>2.093997229567685</v>
       </c>
       <c r="H74">
-        <v>0.2265951373396354</v>
+        <v>0.0366354301613503</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
@@ -3819,6 +3819,11 @@
       <c r="J74" t="inlineStr">
         <is>
           <t>SF_early</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>*</t>
         </is>
       </c>
     </row>
@@ -3839,19 +3844,19 @@
         </is>
       </c>
       <c r="D75">
-        <v>-0.2037609963710457</v>
+        <v>-0.2090552724077248</v>
       </c>
       <c r="E75">
-        <v>0.02891681708520619</v>
+        <v>0.01886262630137222</v>
       </c>
       <c r="F75">
-        <v>709.9961706954797</v>
+        <v>670</v>
       </c>
       <c r="G75">
-        <v>7.046453133850943</v>
+        <v>11.08304162249752</v>
       </c>
       <c r="H75">
-        <v>1.305248537527337E-11</v>
+        <v>1.504533145489525E-25</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
@@ -3886,19 +3891,19 @@
         </is>
       </c>
       <c r="D76">
-        <v>-0.2298349251436343</v>
+        <v>-0.2751746905536586</v>
       </c>
       <c r="E76">
-        <v>0.03243734127430564</v>
+        <v>0.02611570697124655</v>
       </c>
       <c r="F76">
-        <v>710.0163590209673</v>
+        <v>670</v>
       </c>
       <c r="G76">
-        <v>7.085504425286911</v>
+        <v>10.53675057912951</v>
       </c>
       <c r="H76">
-        <v>1.305248537527337E-11</v>
+        <v>1.197643860331968E-23</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
@@ -3933,19 +3938,19 @@
         </is>
       </c>
       <c r="D77">
-        <v>0.1715664947485203</v>
+        <v>0.2047493117322805</v>
       </c>
       <c r="E77">
-        <v>0.0289168170852062</v>
+        <v>0.01758304294825129</v>
       </c>
       <c r="F77">
-        <v>709.9961706944198</v>
+        <v>670</v>
       </c>
       <c r="G77">
-        <v>-5.933104402292375</v>
+        <v>-11.64470292968509</v>
       </c>
       <c r="H77">
-        <v>9.289756326569897E-09</v>
+        <v>6.853117697902203E-28</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
@@ -3980,19 +3985,19 @@
         </is>
       </c>
       <c r="D78">
-        <v>-0.05504208856404916</v>
+        <v>-0.04335281674373848</v>
       </c>
       <c r="E78">
-        <v>0.0289168170852062</v>
+        <v>0.02009050984142178</v>
       </c>
       <c r="F78">
-        <v>709.9961706954796</v>
+        <v>670</v>
       </c>
       <c r="G78">
-        <v>1.903462901946031</v>
+        <v>2.157875389222599</v>
       </c>
       <c r="H78">
-        <v>0.07930154516790007</v>
+        <v>0.03755064168427239</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
@@ -4002,6 +4007,11 @@
       <c r="J78" t="inlineStr">
         <is>
           <t>SF_intermediate</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>*</t>
         </is>
       </c>
     </row>
@@ -4022,19 +4032,19 @@
         </is>
       </c>
       <c r="D79">
-        <v>-0.0597069750243481</v>
+        <v>-0.09696173950508552</v>
       </c>
       <c r="E79">
-        <v>0.03243734127430564</v>
+        <v>0.02358949522447025</v>
       </c>
       <c r="F79">
-        <v>710.0163590208424</v>
+        <v>670</v>
       </c>
       <c r="G79">
-        <v>1.840686464387985</v>
+        <v>4.110377885682927</v>
       </c>
       <c r="H79">
-        <v>0.07930154516790007</v>
+        <v>6.660307892623015E-05</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
@@ -4044,6 +4054,11 @@
       <c r="J79" t="inlineStr">
         <is>
           <t>SF_advanced</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>*</t>
         </is>
       </c>
     </row>
@@ -4064,19 +4079,19 @@
         </is>
       </c>
       <c r="D80">
-        <v>0.130326806554436</v>
+        <v>0.1869286868528317</v>
       </c>
       <c r="E80">
-        <v>0.02891681708520618</v>
+        <v>0.02376986094717347</v>
       </c>
       <c r="F80">
-        <v>709.9961706943607</v>
+        <v>670</v>
       </c>
       <c r="G80">
-        <v>-4.506955456764675</v>
+        <v>-7.864105190529514</v>
       </c>
       <c r="H80">
-        <v>1.537995416274119E-05</v>
+        <v>8.944116711803431E-14</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
@@ -4111,19 +4126,19 @@
         </is>
       </c>
       <c r="D81">
-        <v>-0.04809591686294631</v>
+        <v>-0.0435083149989689</v>
       </c>
       <c r="E81">
-        <v>0.02891681708520618</v>
+        <v>0.02600178076698922</v>
       </c>
       <c r="F81">
-        <v>709.9961706967566</v>
+        <v>670</v>
       </c>
       <c r="G81">
-        <v>1.663250720894595</v>
+        <v>1.673282125899825</v>
       </c>
       <c r="H81">
-        <v>0.1160442834791523</v>
+        <v>0.09473855299429551</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
@@ -4153,19 +4168,19 @@
         </is>
       </c>
       <c r="D82">
-        <v>-0.07105670867610671</v>
+        <v>-0.1347501436441985</v>
       </c>
       <c r="E82">
-        <v>0.03243734127430562</v>
+        <v>0.03647777145753643</v>
       </c>
       <c r="F82">
-        <v>710.0163590208666</v>
+        <v>670</v>
       </c>
       <c r="G82">
-        <v>2.190583626297153</v>
+        <v>3.69403442863993</v>
       </c>
       <c r="H82">
-        <v>0.04320953923740183</v>
+        <v>0.0003580883225887132</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
@@ -4200,19 +4215,19 @@
         </is>
       </c>
       <c r="D83">
-        <v>0.1672261259468699</v>
+        <v>0.2216737840904148</v>
       </c>
       <c r="E83">
-        <v>0.02891681708520619</v>
+        <v>0.02365983620554312</v>
       </c>
       <c r="F83">
-        <v>709.9961706948853</v>
+        <v>670</v>
       </c>
       <c r="G83">
-        <v>-5.78300597379449</v>
+        <v>-9.369201974377159</v>
       </c>
       <c r="H83">
-        <v>3.299146664071083E-08</v>
+        <v>6.574987117761472E-19</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
@@ -4247,19 +4262,19 @@
         </is>
       </c>
       <c r="D84">
-        <v>-0.02799895194908212</v>
+        <v>-0.01280787380511128</v>
       </c>
       <c r="E84">
-        <v>0.02891681708520619</v>
+        <v>0.02561315787962174</v>
       </c>
       <c r="F84">
-        <v>709.9961706972845</v>
+        <v>670</v>
       </c>
       <c r="G84">
-        <v>0.9682584312990086</v>
+        <v>0.5000505546917134</v>
       </c>
       <c r="H84">
-        <v>0.3332450294794945</v>
+        <v>0.6172036714970247</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
@@ -4289,19 +4304,19 @@
         </is>
       </c>
       <c r="D85">
-        <v>0.1225457849472958</v>
+        <v>0.09229865517009417</v>
       </c>
       <c r="E85">
-        <v>0.03243734127430564</v>
+        <v>0.02358942012630007</v>
       </c>
       <c r="F85">
-        <v>710.0163590208363</v>
+        <v>670</v>
       </c>
       <c r="G85">
-        <v>-3.777923224686948</v>
+        <v>-3.912714033491205</v>
       </c>
       <c r="H85">
-        <v>0.0002571000266844896</v>
+        <v>0.0001508711239087287</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
@@ -4336,19 +4351,19 @@
         </is>
       </c>
       <c r="D86">
-        <v>0.1368250642686012</v>
+        <v>0.1547072650095783</v>
       </c>
       <c r="E86">
-        <v>0.02891681708520618</v>
+        <v>0.02431706685698331</v>
       </c>
       <c r="F86">
-        <v>709.9961706935278</v>
+        <v>670</v>
       </c>
       <c r="G86">
-        <v>-4.731677897516624</v>
+        <v>-6.362085769614517</v>
       </c>
       <c r="H86">
-        <v>1.023233913218465E-05</v>
+        <v>2.212769178361133E-09</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
@@ -4383,19 +4398,19 @@
         </is>
       </c>
       <c r="D87">
-        <v>0.001449205066081483</v>
+        <v>-0.004369043913614923</v>
       </c>
       <c r="E87">
-        <v>0.02891681708520618</v>
+        <v>0.01753618705602045</v>
       </c>
       <c r="F87">
-        <v>709.996170695711</v>
+        <v>670</v>
       </c>
       <c r="G87">
-        <v>-0.05011634101399409</v>
+        <v>0.2491444633692454</v>
       </c>
       <c r="H87">
-        <v>0.9600437730381409</v>
+        <v>0.8033253934425596</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
@@ -4425,19 +4440,19 @@
         </is>
       </c>
       <c r="D88">
-        <v>0.02689578418489549</v>
+        <v>0.01140042929904039</v>
       </c>
       <c r="E88">
-        <v>0.03243734127430562</v>
+        <v>0.02494904335992693</v>
       </c>
       <c r="F88">
-        <v>710.0163590210262</v>
+        <v>670</v>
       </c>
       <c r="G88">
-        <v>-0.8291611805496609</v>
+        <v>-0.4569485544825228</v>
       </c>
       <c r="H88">
-        <v>0.5196212933648304</v>
+        <v>0.7774273624368495</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
@@ -4467,19 +4482,19 @@
         </is>
       </c>
       <c r="D89">
-        <v>-0.06922301444867088</v>
+        <v>0.04590225299907302</v>
       </c>
       <c r="E89">
-        <v>0.02891681708520618</v>
+        <v>0.04333348648297706</v>
       </c>
       <c r="F89">
-        <v>709.996170694121</v>
+        <v>670</v>
       </c>
       <c r="G89">
-        <v>2.393867009799129</v>
+        <v>-1.059279017789281</v>
       </c>
       <c r="H89">
-        <v>0.02539550636717143</v>
+        <v>0.2898544549199381</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
@@ -4489,11 +4504,6 @@
       <c r="J89" t="inlineStr">
         <is>
           <t>SF_early</t>
-        </is>
-      </c>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t>*</t>
         </is>
       </c>
     </row>
@@ -4514,19 +4524,19 @@
         </is>
       </c>
       <c r="D90">
-        <v>-0.2027029241609409</v>
+        <v>-0.1816233232974297</v>
       </c>
       <c r="E90">
-        <v>0.02891681708520618</v>
+        <v>0.02201248127629837</v>
       </c>
       <c r="F90">
-        <v>709.9961706967042</v>
+        <v>670</v>
       </c>
       <c r="G90">
-        <v>7.009862930752623</v>
+        <v>8.250924601262016</v>
       </c>
       <c r="H90">
-        <v>3.335594587793137E-11</v>
+        <v>5.002031467608283E-15</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
@@ -4561,19 +4571,19 @@
         </is>
       </c>
       <c r="D91">
-        <v>-0.0401644910285189</v>
+        <v>-0.04249953084534669</v>
       </c>
       <c r="E91">
-        <v>0.03243734127430562</v>
+        <v>0.02414429054112859</v>
       </c>
       <c r="F91">
-        <v>710.0163590213001</v>
+        <v>670</v>
       </c>
       <c r="G91">
-        <v>1.238217728415804</v>
+        <v>1.760231089538575</v>
       </c>
       <c r="H91">
-        <v>0.2592535031244493</v>
+        <v>0.09458985741704834</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
